--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_2구역_ver3.4.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_2구역_ver3.4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200013\Desktop\프로젝트HI\2_Documents\데이터 테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B6BC5A-4E0B-4D27-B61A-34A09D5B74AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C325AB0B-E8A5-4237-9764-0FB810C84C63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개요" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="934">
   <si>
     <t>이벤트 스크립트 테이블</t>
   </si>
@@ -1917,15 +1917,9 @@
     <t>증폭기를 우선 제압한다. 최종전 재개.</t>
   </si>
   <si>
-    <t>(최종 재전투가 시작되었다.)</t>
-  </si>
-  <si>
     <t>아놀드</t>
   </si>
   <si>
-    <t>아놀드. 출동한다.</t>
-  </si>
-  <si>
     <t>아놀드! 이번에야말로 다 박살내버려!</t>
   </si>
   <si>
@@ -1941,9 +1935,6 @@
     <t>(UMT와 마주쳤다.)</t>
   </si>
   <si>
-    <t xml:space="preserve">이번에야말로 </t>
-  </si>
-  <si>
     <t>1A</t>
   </si>
   <si>
@@ -1962,16 +1953,10 @@
     <t>시위대를 돕는다</t>
   </si>
   <si>
-    <t>Set_Flag_MainQuest3-1HelpProtesters</t>
-  </si>
-  <si>
     <t>행동 선택 / 시위대 협조</t>
   </si>
   <si>
     <t>둘 다 제압한다</t>
-  </si>
-  <si>
-    <t>Set_Flag_MainQuest3-1Subjugation</t>
   </si>
   <si>
     <t>행동 선택 / 전원 토벌</t>
@@ -2041,9 +2026,6 @@
   </si>
   <si>
     <t>메인 퀘스트 3-1 최초 패배 보상 / 재전투 해금</t>
-  </si>
-  <si>
-    <t>Set_Flag_MainQuest3-1RetryAvailable</t>
   </si>
   <si>
     <t>메인 퀘스트 3-1 재패배 / 보상 중복 지급 방지</t>
@@ -2889,6 +2871,353 @@
   </si>
   <si>
     <t>로니와 만남(메인 3-2 완료)</t>
+  </si>
+  <si>
+    <t>이번에야말로 없애주겠다.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flag_MainQuest3-2Complete==1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_MainQuest3-1RetryAvailable</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start_BE401</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_MainQuest3-1HelpProtesters</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flag_MainQuest3-1Complete==1\
+Flag_MainQuest3-1HelpProtesters</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>2C</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>3C</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>시위대 보호(메인 3-1 완료)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 토벌(메인 3-1 완료)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_MainQuest3-1Subjugation</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flag_MainQuest3-1Complete==1\
+Flag_MainQuest3-1Subjugation</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>루미나</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>저스티스</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>아놀드</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐지?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀석을 안 뒤로 쟤를 보니 기분이 이상해졌어.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>블랙불릿</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>나도…</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>네코밍</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 동생을 만났나?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 승리</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 진입</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start_BE261</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐라?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>감히 그 신성한 이름을 그 더러운 입에 담다니!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떻게 친위대 이름이 율리아 마지 텐시…</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>타고난 체질에 반해 파리 하나 못 죽이는 연약한 놈이지.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭주하는 아놀드와 함께 UMT와 전투에 들어갔다.)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사를 좀먹으려는 벌레들을 구하겠답시고 내 부하들을 괴롭히다니!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>네놈들의 정신상태를 단련시켜주마!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>용서 못한다!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>올바른 대우를 받는 것에 어디가 잘못되었단 말이냐!!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔직히 그건 우리도 찔리긴 해.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉿!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇지.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 이놈!!!!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>시위대고 뭐고 안 가리고 내 부하들까지 괴롭혔다지?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>네놈들 눈엔 다 똑같은 짐승에 불과하더냐!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>네놈들의 썩어빠진 정신상태를 단련시켜주마!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>다 똑같은 빌런 아닌가요?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>썩은 건 네 근육으로 가득 찬 뇌겠지! 단련은 너나 해!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>…죽어라.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그치만 같다고 한 건 당신인데…</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>시끄럽다! 누가 너와 같다는 거냐!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 무능한 애들한테 진 넌 사는 게 사치인 건가?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>밥만 축내는 머저리들이 누구한테 무능하다는 거냐!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>정곡이군.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런가요…</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래 우린 별로 다르지 않-</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>무능하고, 남에게 민폐만 끼치는 주제에 하는 일마다 사고만 일으키고, 밥만 축내며 하루하루 허송세월 보내는 게 차라리 도움이 되는-</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>어, 그건-</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 지긋지긋한 녀석들이군.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌런이 할 말은 아니네!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥, 빌런이지. 나는 포악하며, 힘으로 약탈하는 걸 즐긴다.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러나 스스로 정의롭다며 사람을 해치고 희열을 느끼는 너희도 무엇이 다른가!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>싫어! 너나 죽어!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 종료</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>1A</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 패배</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼마든지 받아주마!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>오지마!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>크아악! 다시 돌아오겠다!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>두번 다시 못 걸어다니게 만들어주지!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UMT를 격퇴했다.)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>받아라. 연막킥!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>4A</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flag_UMT2RetryAvailable==1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에야말로 박살내주마!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>...쟤 원래 저런 성격이었어?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>패배로 단련된 우리 애들이 얌전히 잡힐 줄 알고?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>(아놀드의 안면에 연막탄을 날린 사이 쓰러진 히어로들을 수습해 협회로 복귀했다.)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>아놀드. 출동한다!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>(UMT가 등장했다.)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 승리 보상</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 싫다 정말…</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>히어로! 죽인다!</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>(극한으로 치솟은 분노로 지능이 퇴화한 모양이다.)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>UMT 재등장</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>UMT 최초 등장</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_207001\
+Set_Flag_UMT2Clear</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flag_UMT2Clear</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_UMT2RetryAvailable</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>재전투</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>(최종 전투가 시작되었다.)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3020,7 +3349,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3035,6 +3364,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3277,7 +3612,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3465,29 +3800,39 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3500,6 +3845,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3580,8 +3937,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>433821</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>151898</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1981200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3603,6 +3960,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7518776" y="31591380"/>
+          <a:ext cx="11660245" cy="7842120"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -3865,191 +4226,191 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
+      <c r="B2" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="73"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="87"/>
+      <c r="L8" s="87"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="87"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
     </row>
     <row r="16" spans="2:12" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="21"/>
@@ -4313,10 +4674,10 @@
         <v>15</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="26.25" x14ac:dyDescent="0.5">
@@ -4363,13 +4724,13 @@
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="79" t="s">
         <v>58</v>
       </c>
       <c r="E36" s="7" t="s">
@@ -4377,41 +4738,41 @@
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
       <c r="E37" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
       <c r="E39" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
       <c r="E40" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
       <c r="E41" s="10" t="s">
         <v>65</v>
       </c>
@@ -4557,13 +4918,13 @@
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B54" s="75" t="s">
+      <c r="B54" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="77" t="s">
+      <c r="C54" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="77" t="s">
+      <c r="D54" s="81" t="s">
         <v>98</v>
       </c>
       <c r="E54" s="7" t="s">
@@ -4571,37 +4932,37 @@
       </c>
     </row>
     <row r="55" spans="2:5" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B55" s="80"/>
-      <c r="C55" s="78"/>
-      <c r="D55" s="78"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
       <c r="E55" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="80"/>
-      <c r="C56" s="78"/>
-      <c r="D56" s="78"/>
+      <c r="B56" s="84"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
       <c r="E56" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="76"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="79"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
       <c r="E57" s="14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B58" s="75" t="s">
+      <c r="B58" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="77" t="s">
+      <c r="C58" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="D58" s="77" t="s">
+      <c r="D58" s="81" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="7" t="s">
@@ -4609,9 +4970,9 @@
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B59" s="76"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="79"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
       <c r="E59" s="11" t="s">
         <v>106</v>
       </c>
@@ -4645,13 +5006,13 @@
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B62" s="75" t="s">
+      <c r="B62" s="77" t="s">
         <v>114</v>
       </c>
-      <c r="C62" s="69" t="s">
+      <c r="C62" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="D62" s="69" t="s">
+      <c r="D62" s="79" t="s">
         <v>69</v>
       </c>
       <c r="E62" s="7" t="s">
@@ -4659,15 +5020,23 @@
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B63" s="76"/>
-      <c r="C63" s="71"/>
-      <c r="D63" s="71"/>
+      <c r="B63" s="78"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="11" t="s">
         <v>117</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="D36:D41"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="B2:L10"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C16:L16"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="C62:C63"/>
     <mergeCell ref="D62:D63"/>
@@ -4677,14 +5046,6 @@
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
     <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="D36:D41"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="B2:L10"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="C16:L16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4736,307 +5097,307 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="99" x14ac:dyDescent="0.3">
-      <c r="B5" s="81" t="s">
-        <v>814</v>
+      <c r="B5" s="89" t="s">
+        <v>808</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>126</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="115.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="82"/>
+      <c r="B6" s="90"/>
       <c r="C6" s="25" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="82"/>
+      <c r="B7" s="90"/>
       <c r="C7" s="25" t="s">
         <v>130</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="83"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="25" t="s">
         <v>132</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="81" t="s">
-        <v>819</v>
+      <c r="B9" s="89" t="s">
+        <v>813</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="82"/>
+      <c r="B10" s="90"/>
       <c r="C10" s="25" t="s">
         <v>136</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="82"/>
+      <c r="B11" s="90"/>
       <c r="C11" s="25" t="s">
         <v>138</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="83"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="25" t="s">
         <v>140</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="B13" s="81" t="s">
-        <v>824</v>
+      <c r="B13" s="89" t="s">
+        <v>818</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="B14" s="82"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="25" t="s">
         <v>144</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="B15" s="82"/>
+      <c r="B15" s="90"/>
       <c r="C15" s="25" t="s">
         <v>146</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="83"/>
+      <c r="B16" s="91"/>
       <c r="C16" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="165" x14ac:dyDescent="0.3">
-      <c r="B17" s="81" t="s">
-        <v>829</v>
+      <c r="B17" s="89" t="s">
+        <v>823</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>150</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="82"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="82"/>
+      <c r="B19" s="90"/>
       <c r="C19" s="25" t="s">
         <v>153</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="83"/>
+      <c r="B20" s="91"/>
       <c r="C20" s="25" t="s">
         <v>155</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="115.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="81" t="s">
-        <v>835</v>
+      <c r="B21" s="89" t="s">
+        <v>829</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>157</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="82"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="25" t="s">
         <v>158</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="82"/>
+      <c r="B23" s="90"/>
       <c r="C23" s="25" t="s">
         <v>160</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="83"/>
+      <c r="B24" s="91"/>
       <c r="C24" s="25" t="s">
         <v>162</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="81" t="s">
-        <v>841</v>
+      <c r="B25" s="89" t="s">
+        <v>835</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>164</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="82"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="25" t="s">
         <v>166</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="82"/>
+      <c r="B27" s="90"/>
       <c r="C27" s="25" t="s">
         <v>168</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="83"/>
+      <c r="B28" s="91"/>
       <c r="C28" s="25" t="s">
         <v>170</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="89" t="s">
         <v>172</v>
       </c>
       <c r="C29" s="25" t="s">
@@ -5048,7 +5409,7 @@
       <c r="E29" s="31"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="82"/>
+      <c r="B30" s="90"/>
       <c r="C30" s="25" t="s">
         <v>175</v>
       </c>
@@ -5058,7 +5419,7 @@
       <c r="E30" s="31"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="82"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="25" t="s">
         <v>177</v>
       </c>
@@ -5068,7 +5429,7 @@
       <c r="E31" s="31"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="83"/>
+      <c r="B32" s="91"/>
       <c r="C32" s="25" t="s">
         <v>179</v>
       </c>
@@ -5078,7 +5439,7 @@
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="81" t="s">
+      <c r="B33" s="89" t="s">
         <v>181</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -5090,7 +5451,7 @@
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="82"/>
+      <c r="B34" s="90"/>
       <c r="C34" s="25" t="s">
         <v>184</v>
       </c>
@@ -5100,7 +5461,7 @@
       <c r="E34" s="30"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="82"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="25" t="s">
         <v>186</v>
       </c>
@@ -5110,7 +5471,7 @@
       <c r="E35" s="26"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="83"/>
+      <c r="B36" s="91"/>
       <c r="C36" s="25" t="s">
         <v>188</v>
       </c>
@@ -5184,7 +5545,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H674"/>
+  <dimension ref="A1:I670"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -11989,7 +12350,7 @@
       </c>
       <c r="H352" s="32"/>
     </row>
-    <row r="353" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="32">
         <v>4240030</v>
       </c>
@@ -12007,7 +12368,7 @@
       </c>
       <c r="H353" s="32"/>
     </row>
-    <row r="354" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="32">
         <v>4240040</v>
       </c>
@@ -12025,7 +12386,7 @@
         <v>42401</v>
       </c>
     </row>
-    <row r="355" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="32">
         <v>4250010</v>
       </c>
@@ -12038,10 +12399,12 @@
         <v>544</v>
       </c>
       <c r="F355" s="32"/>
-      <c r="G355" s="32"/>
+      <c r="G355" s="32">
+        <v>4250020</v>
+      </c>
       <c r="H355" s="32"/>
     </row>
-    <row r="356" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="32">
         <v>4250020</v>
       </c>
@@ -12061,7 +12424,7 @@
       </c>
       <c r="H356" s="32"/>
     </row>
-    <row r="357" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="32">
         <v>4250030</v>
       </c>
@@ -12081,7 +12444,7 @@
       </c>
       <c r="H357" s="32"/>
     </row>
-    <row r="358" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="32">
         <v>4250040</v>
       </c>
@@ -12099,7 +12462,7 @@
       </c>
       <c r="H358" s="32"/>
     </row>
-    <row r="359" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="32">
         <v>4250050</v>
       </c>
@@ -12109,7 +12472,7 @@
       <c r="C359" s="32"/>
       <c r="D359" s="32"/>
       <c r="E359" s="33" t="s">
-        <v>548</v>
+        <v>933</v>
       </c>
       <c r="F359" s="32"/>
       <c r="G359" s="32">
@@ -12119,7 +12482,7 @@
         <v>42501</v>
       </c>
     </row>
-    <row r="360" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="32">
         <v>4259001</v>
       </c>
@@ -12137,103 +12500,103 @@
         <v>42502</v>
       </c>
     </row>
-    <row r="361" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="25">
+    <row r="361" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A361" s="74">
         <v>4360010</v>
       </c>
-      <c r="B361" s="32">
-        <v>0</v>
-      </c>
-      <c r="C361" s="32" t="s">
-        <v>549</v>
-      </c>
-      <c r="D361" s="32"/>
-      <c r="E361" s="33" t="s">
-        <v>550</v>
+      <c r="B361" s="51">
+        <v>2</v>
+      </c>
+      <c r="E361" s="36" t="s">
+        <v>922</v>
       </c>
       <c r="F361" s="32"/>
-      <c r="G361" s="25">
-        <v>4360020</v>
-      </c>
-      <c r="H361" s="32"/>
-    </row>
-    <row r="362" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H361" s="73">
+        <v>43605</v>
+      </c>
+      <c r="I361" s="35"/>
+    </row>
+    <row r="362" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="25">
-        <v>4360020</v>
+        <v>4360011</v>
       </c>
       <c r="B362" s="32">
         <v>0</v>
       </c>
       <c r="C362" s="32" t="s">
-        <v>205</v>
+        <v>548</v>
       </c>
       <c r="D362" s="32"/>
       <c r="E362" s="33" t="s">
-        <v>551</v>
+        <v>921</v>
       </c>
       <c r="F362" s="32"/>
       <c r="G362" s="25">
-        <v>4360030</v>
+        <v>4360020</v>
       </c>
       <c r="H362" s="32"/>
     </row>
-    <row r="363" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="25">
-        <v>4360030</v>
+        <v>4360020</v>
       </c>
       <c r="B363" s="32">
-        <v>1</v>
-      </c>
-      <c r="C363" s="32"/>
+        <v>0</v>
+      </c>
+      <c r="C363" s="32" t="s">
+        <v>205</v>
+      </c>
       <c r="D363" s="32"/>
       <c r="E363" s="33" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F363" s="32"/>
       <c r="G363" s="25">
-        <v>4360040</v>
+        <v>4360030</v>
       </c>
       <c r="H363" s="32"/>
     </row>
-    <row r="364" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="25">
-        <v>4360040</v>
+        <v>4360030</v>
       </c>
       <c r="B364" s="32">
-        <v>0</v>
-      </c>
-      <c r="C364" s="32" t="s">
-        <v>549</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C364" s="32"/>
       <c r="D364" s="32"/>
       <c r="E364" s="33" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F364" s="32"/>
       <c r="G364" s="25">
-        <v>4360050</v>
+        <v>4360040</v>
       </c>
       <c r="H364" s="32"/>
     </row>
-    <row r="365" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="25">
-        <v>4360050</v>
+        <v>4360040</v>
       </c>
       <c r="B365" s="32">
-        <v>2</v>
-      </c>
-      <c r="C365" s="32"/>
+        <v>0</v>
+      </c>
+      <c r="C365" s="32" t="s">
+        <v>548</v>
+      </c>
       <c r="D365" s="32"/>
       <c r="E365" s="33" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F365" s="32"/>
-      <c r="G365" s="32"/>
+      <c r="G365" s="25">
+        <v>4360050</v>
+      </c>
       <c r="H365" s="32"/>
     </row>
-    <row r="366" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="25">
-        <v>4361010</v>
+        <v>4360050</v>
       </c>
       <c r="B366" s="32">
         <v>2</v>
@@ -12241,626 +12604,1167 @@
       <c r="C366" s="32"/>
       <c r="D366" s="32"/>
       <c r="E366" s="33" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F366" s="32"/>
-      <c r="G366" s="32"/>
+      <c r="G366" s="25"/>
       <c r="H366" s="32"/>
     </row>
-    <row r="367" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="25">
-        <v>4361020</v>
+    <row r="367" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A367" s="74">
+        <v>4361010</v>
       </c>
       <c r="B367" s="32">
-        <v>0</v>
-      </c>
-      <c r="C367" s="32" t="s">
-        <v>549</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C367" s="32"/>
       <c r="D367" s="32"/>
       <c r="E367" s="33" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F367" s="32"/>
       <c r="G367" s="32"/>
-      <c r="H367" s="32"/>
-    </row>
-    <row r="368" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="32"/>
-      <c r="B368" s="32"/>
-      <c r="C368" s="32"/>
+      <c r="H367" s="32">
+        <v>43601</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A368" s="25">
+        <v>4361020</v>
+      </c>
+      <c r="B368" s="32">
+        <v>0</v>
+      </c>
+      <c r="C368" s="32" t="s">
+        <v>548</v>
+      </c>
       <c r="D368" s="32"/>
-      <c r="E368" s="33"/>
+      <c r="E368" s="33" t="s">
+        <v>848</v>
+      </c>
       <c r="F368" s="32"/>
-      <c r="G368" s="32"/>
+      <c r="G368" s="25">
+        <v>4361030</v>
+      </c>
       <c r="H368" s="32"/>
     </row>
-    <row r="369" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="32"/>
-      <c r="B369" s="32"/>
-      <c r="C369" s="32"/>
+    <row r="369" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A369" s="25">
+        <v>4361030</v>
+      </c>
+      <c r="B369" s="32">
+        <v>0</v>
+      </c>
+      <c r="C369" s="32" t="s">
+        <v>860</v>
+      </c>
       <c r="D369" s="32"/>
-      <c r="E369" s="33"/>
+      <c r="E369" s="33" t="s">
+        <v>861</v>
+      </c>
       <c r="F369" s="32"/>
-      <c r="G369" s="32"/>
+      <c r="G369" s="25">
+        <v>4361040</v>
+      </c>
       <c r="H369" s="32"/>
     </row>
-    <row r="370" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="32"/>
-      <c r="B370" s="32"/>
-      <c r="C370" s="32"/>
+    <row r="370" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A370" s="25">
+        <v>4361040</v>
+      </c>
+      <c r="B370" s="32">
+        <v>0</v>
+      </c>
+      <c r="C370" s="32" t="s">
+        <v>862</v>
+      </c>
       <c r="D370" s="32"/>
-      <c r="E370" s="33"/>
+      <c r="E370" s="33" t="s">
+        <v>861</v>
+      </c>
       <c r="F370" s="32"/>
-      <c r="G370" s="32"/>
+      <c r="G370" s="25">
+        <v>4361050</v>
+      </c>
       <c r="H370" s="32"/>
     </row>
-    <row r="371" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="32"/>
-      <c r="B371" s="32"/>
-      <c r="C371" s="32"/>
+    <row r="371" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A371" s="25">
+        <v>4361050</v>
+      </c>
+      <c r="B371" s="32">
+        <v>0</v>
+      </c>
+      <c r="C371" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D371" s="32"/>
-      <c r="E371" s="33"/>
+      <c r="E371" s="33" t="s">
+        <v>864</v>
+      </c>
       <c r="F371" s="32"/>
-      <c r="G371" s="32"/>
+      <c r="G371" s="25">
+        <v>4361060</v>
+      </c>
       <c r="H371" s="32"/>
     </row>
-    <row r="372" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="32"/>
-      <c r="B372" s="32"/>
+    <row r="372" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A372" s="25">
+        <v>4361060</v>
+      </c>
+      <c r="B372" s="32">
+        <v>1</v>
+      </c>
       <c r="C372" s="32"/>
       <c r="D372" s="32"/>
-      <c r="E372" s="33"/>
+      <c r="E372" s="36" t="s">
+        <v>865</v>
+      </c>
       <c r="F372" s="32"/>
-      <c r="G372" s="32"/>
+      <c r="G372" s="25">
+        <v>4361070</v>
+      </c>
       <c r="H372" s="32"/>
     </row>
-    <row r="373" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="32"/>
-      <c r="B373" s="32"/>
-      <c r="C373" s="32"/>
+    <row r="373" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A373" s="25">
+        <v>4361070</v>
+      </c>
+      <c r="B373" s="32">
+        <v>0</v>
+      </c>
+      <c r="C373" s="32" t="s">
+        <v>866</v>
+      </c>
       <c r="D373" s="32"/>
-      <c r="E373" s="33"/>
+      <c r="E373" s="33" t="s">
+        <v>867</v>
+      </c>
       <c r="F373" s="32"/>
-      <c r="G373" s="32"/>
+      <c r="G373" s="25">
+        <v>4361080</v>
+      </c>
       <c r="H373" s="32"/>
     </row>
-    <row r="374" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="32"/>
-      <c r="B374" s="32"/>
-      <c r="C374" s="32"/>
+    <row r="374" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A374" s="25">
+        <v>4361080</v>
+      </c>
+      <c r="B374" s="32">
+        <v>0</v>
+      </c>
+      <c r="C374" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D374" s="32"/>
-      <c r="E374" s="33"/>
+      <c r="E374" s="33" t="s">
+        <v>869</v>
+      </c>
       <c r="F374" s="32"/>
-      <c r="G374" s="32"/>
+      <c r="G374" s="25">
+        <v>4361090</v>
+      </c>
       <c r="H374" s="32"/>
     </row>
-    <row r="375" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="32"/>
-      <c r="B375" s="32"/>
-      <c r="C375" s="32"/>
+    <row r="375" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A375" s="25">
+        <v>4361090</v>
+      </c>
+      <c r="B375" s="32">
+        <v>0</v>
+      </c>
+      <c r="C375" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D375" s="32"/>
-      <c r="E375" s="33"/>
+      <c r="E375" s="33" t="s">
+        <v>876</v>
+      </c>
       <c r="F375" s="32"/>
-      <c r="G375" s="32"/>
+      <c r="G375" s="25">
+        <v>4361100</v>
+      </c>
       <c r="H375" s="32"/>
     </row>
-    <row r="376" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="32"/>
-      <c r="B376" s="32"/>
-      <c r="C376" s="32"/>
+    <row r="376" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A376" s="25">
+        <v>4361100</v>
+      </c>
+      <c r="B376" s="32">
+        <v>0</v>
+      </c>
+      <c r="C376" s="32" t="s">
+        <v>868</v>
+      </c>
       <c r="D376" s="32"/>
-      <c r="E376" s="33"/>
+      <c r="E376" s="33" t="s">
+        <v>875</v>
+      </c>
       <c r="F376" s="32"/>
-      <c r="G376" s="32"/>
+      <c r="G376" s="25">
+        <v>4361110</v>
+      </c>
       <c r="H376" s="32"/>
     </row>
-    <row r="377" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="32"/>
-      <c r="B377" s="32"/>
-      <c r="C377" s="32"/>
-      <c r="D377" s="32"/>
-      <c r="E377" s="33"/>
+    <row r="377" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="25">
+        <v>4361110</v>
+      </c>
+      <c r="B377" s="32">
+        <v>0</v>
+      </c>
+      <c r="C377" s="51" t="s">
+        <v>863</v>
+      </c>
+      <c r="E377" s="36" t="s">
+        <v>873</v>
+      </c>
       <c r="F377" s="32"/>
-      <c r="G377" s="32"/>
+      <c r="G377" s="25">
+        <v>4361120</v>
+      </c>
       <c r="H377" s="32"/>
     </row>
-    <row r="378" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="32"/>
-      <c r="B378" s="32"/>
-      <c r="C378" s="32"/>
+    <row r="378" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="25">
+        <v>4361120</v>
+      </c>
+      <c r="B378" s="32">
+        <v>0</v>
+      </c>
+      <c r="C378" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D378" s="32"/>
-      <c r="E378" s="33"/>
+      <c r="E378" s="33" t="s">
+        <v>874</v>
+      </c>
       <c r="F378" s="32"/>
-      <c r="G378" s="32"/>
+      <c r="G378" s="25">
+        <v>4361130</v>
+      </c>
       <c r="H378" s="32"/>
     </row>
-    <row r="379" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="32"/>
-      <c r="B379" s="32"/>
-      <c r="C379" s="32"/>
+    <row r="379" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A379" s="25">
+        <v>4361130</v>
+      </c>
+      <c r="B379" s="32">
+        <v>0</v>
+      </c>
+      <c r="C379" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D379" s="32"/>
-      <c r="E379" s="33"/>
+      <c r="E379" s="33" t="s">
+        <v>879</v>
+      </c>
       <c r="F379" s="32"/>
-      <c r="G379" s="32"/>
+      <c r="G379" s="25">
+        <v>4361140</v>
+      </c>
       <c r="H379" s="32"/>
     </row>
-    <row r="380" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="32"/>
-      <c r="B380" s="32"/>
-      <c r="C380" s="32"/>
-      <c r="D380" s="32"/>
-      <c r="E380" s="33"/>
+    <row r="380" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="25">
+        <v>4361140</v>
+      </c>
+      <c r="B380" s="32">
+        <v>0</v>
+      </c>
+      <c r="C380" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="E380" s="36" t="s">
+        <v>877</v>
+      </c>
       <c r="F380" s="32"/>
-      <c r="G380" s="32"/>
-      <c r="H380" s="32"/>
-    </row>
-    <row r="381" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="32"/>
-      <c r="B381" s="32"/>
-      <c r="C381" s="32"/>
+      <c r="G380" s="25">
+        <v>4361640</v>
+      </c>
+      <c r="H380" s="32">
+        <v>43602</v>
+      </c>
+      <c r="I380" s="35"/>
+    </row>
+    <row r="381" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A381" s="25">
+        <v>4361210</v>
+      </c>
+      <c r="B381" s="32">
+        <v>0</v>
+      </c>
+      <c r="C381" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D381" s="32"/>
-      <c r="E381" s="33"/>
+      <c r="E381" s="33" t="s">
+        <v>878</v>
+      </c>
       <c r="F381" s="32"/>
-      <c r="G381" s="32"/>
+      <c r="G381" s="25">
+        <v>4361220</v>
+      </c>
       <c r="H381" s="32"/>
     </row>
-    <row r="382" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="32"/>
-      <c r="B382" s="32"/>
-      <c r="C382" s="32"/>
+    <row r="382" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="25">
+        <v>4361220</v>
+      </c>
+      <c r="B382" s="32">
+        <v>0</v>
+      </c>
+      <c r="C382" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D382" s="32"/>
-      <c r="E382" s="33"/>
+      <c r="E382" s="33" t="s">
+        <v>880</v>
+      </c>
       <c r="F382" s="32"/>
-      <c r="G382" s="32"/>
+      <c r="G382" s="25">
+        <v>4361230</v>
+      </c>
       <c r="H382" s="32"/>
     </row>
-    <row r="383" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="32"/>
-      <c r="B383" s="32"/>
-      <c r="C383" s="32"/>
+    <row r="383" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="25">
+        <v>4361230</v>
+      </c>
+      <c r="B383" s="32">
+        <v>0</v>
+      </c>
+      <c r="C383" s="32" t="s">
+        <v>862</v>
+      </c>
       <c r="D383" s="32"/>
-      <c r="E383" s="33"/>
+      <c r="E383" s="33" t="s">
+        <v>881</v>
+      </c>
       <c r="F383" s="32"/>
-      <c r="G383" s="32"/>
+      <c r="G383" s="25">
+        <v>4361240</v>
+      </c>
       <c r="H383" s="32"/>
     </row>
-    <row r="384" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="32"/>
-      <c r="B384" s="32"/>
+    <row r="384" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="25">
+        <v>4361240</v>
+      </c>
+      <c r="B384" s="32">
+        <v>1</v>
+      </c>
       <c r="C384" s="32"/>
       <c r="D384" s="32"/>
-      <c r="E384" s="33"/>
+      <c r="E384" s="33" t="s">
+        <v>882</v>
+      </c>
       <c r="F384" s="32"/>
-      <c r="G384" s="32"/>
+      <c r="G384" s="25">
+        <v>4361250</v>
+      </c>
       <c r="H384" s="32"/>
     </row>
-    <row r="385" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="32"/>
-      <c r="B385" s="32"/>
-      <c r="C385" s="32"/>
+    <row r="385" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="25">
+        <v>4361250</v>
+      </c>
+      <c r="B385" s="32">
+        <v>0</v>
+      </c>
+      <c r="C385" s="32" t="s">
+        <v>866</v>
+      </c>
       <c r="D385" s="32"/>
-      <c r="E385" s="33"/>
+      <c r="E385" s="33" t="s">
+        <v>883</v>
+      </c>
       <c r="F385" s="32"/>
-      <c r="G385" s="32"/>
+      <c r="G385" s="25">
+        <v>4361260</v>
+      </c>
       <c r="H385" s="32"/>
     </row>
-    <row r="386" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="32"/>
-      <c r="B386" s="32"/>
-      <c r="C386" s="32"/>
+    <row r="386" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="25">
+        <v>4361260</v>
+      </c>
+      <c r="B386" s="32">
+        <v>0</v>
+      </c>
+      <c r="C386" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D386" s="32"/>
-      <c r="E386" s="33"/>
+      <c r="E386" s="33" t="s">
+        <v>879</v>
+      </c>
       <c r="F386" s="32"/>
-      <c r="G386" s="32"/>
+      <c r="G386" s="25">
+        <v>4361270</v>
+      </c>
       <c r="H386" s="32"/>
     </row>
-    <row r="387" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="32"/>
-      <c r="B387" s="32"/>
-      <c r="C387" s="32"/>
-      <c r="D387" s="32"/>
-      <c r="E387" s="33"/>
+    <row r="387" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="25">
+        <v>4361270</v>
+      </c>
+      <c r="B387" s="32">
+        <v>0</v>
+      </c>
+      <c r="C387" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="E387" s="36" t="s">
+        <v>877</v>
+      </c>
       <c r="F387" s="32"/>
-      <c r="G387" s="32"/>
-      <c r="H387" s="32"/>
-    </row>
-    <row r="388" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="32"/>
-      <c r="B388" s="32"/>
-      <c r="C388" s="32"/>
+      <c r="G387" s="25">
+        <v>4361640</v>
+      </c>
+      <c r="H387" s="32">
+        <v>43602</v>
+      </c>
+      <c r="I387" s="35"/>
+    </row>
+    <row r="388" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="25">
+        <v>4361310</v>
+      </c>
+      <c r="B388" s="32">
+        <v>0</v>
+      </c>
+      <c r="C388" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D388" s="32"/>
-      <c r="E388" s="33"/>
+      <c r="E388" s="33" t="s">
+        <v>886</v>
+      </c>
       <c r="F388" s="32"/>
-      <c r="G388" s="32"/>
+      <c r="G388" s="25">
+        <v>4361320</v>
+      </c>
       <c r="H388" s="32"/>
     </row>
-    <row r="389" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="32"/>
-      <c r="B389" s="32"/>
-      <c r="C389" s="32"/>
+    <row r="389" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="25">
+        <v>4361320</v>
+      </c>
+      <c r="B389" s="32">
+        <v>0</v>
+      </c>
+      <c r="C389" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D389" s="32"/>
-      <c r="E389" s="33"/>
+      <c r="E389" s="33" t="s">
+        <v>887</v>
+      </c>
       <c r="F389" s="32"/>
-      <c r="G389" s="32"/>
+      <c r="G389" s="25">
+        <v>4361330</v>
+      </c>
       <c r="H389" s="32"/>
     </row>
-    <row r="390" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="32"/>
-      <c r="B390" s="32"/>
-      <c r="C390" s="32"/>
+    <row r="390" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="25">
+        <v>4361330</v>
+      </c>
+      <c r="B390" s="32">
+        <v>0</v>
+      </c>
+      <c r="C390" s="32" t="s">
+        <v>868</v>
+      </c>
       <c r="D390" s="32"/>
-      <c r="E390" s="33"/>
+      <c r="E390" s="33" t="s">
+        <v>889</v>
+      </c>
       <c r="F390" s="32"/>
-      <c r="G390" s="32"/>
+      <c r="G390" s="25">
+        <v>4361340</v>
+      </c>
       <c r="H390" s="32"/>
     </row>
-    <row r="391" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="32"/>
-      <c r="B391" s="32"/>
+    <row r="391" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="25">
+        <v>4361340</v>
+      </c>
+      <c r="B391" s="32">
+        <v>1</v>
+      </c>
       <c r="C391" s="32"/>
       <c r="D391" s="32"/>
-      <c r="E391" s="33"/>
+      <c r="E391" s="33" t="s">
+        <v>884</v>
+      </c>
       <c r="F391" s="32"/>
-      <c r="G391" s="32"/>
+      <c r="G391" s="25">
+        <v>4361350</v>
+      </c>
       <c r="H391" s="32"/>
     </row>
-    <row r="392" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="32"/>
-      <c r="B392" s="32"/>
-      <c r="C392" s="32"/>
+    <row r="392" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="25">
+        <v>4361350</v>
+      </c>
+      <c r="B392" s="32">
+        <v>0</v>
+      </c>
+      <c r="C392" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D392" s="32"/>
-      <c r="E392" s="33"/>
+      <c r="E392" s="33" t="s">
+        <v>885</v>
+      </c>
       <c r="F392" s="32"/>
-      <c r="G392" s="32"/>
+      <c r="G392" s="25">
+        <v>4361360</v>
+      </c>
       <c r="H392" s="32"/>
     </row>
-    <row r="393" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="32"/>
-      <c r="B393" s="32"/>
-      <c r="C393" s="32"/>
+    <row r="393" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="25">
+        <v>4361360</v>
+      </c>
+      <c r="B393" s="32">
+        <v>0</v>
+      </c>
+      <c r="C393" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D393" s="32"/>
-      <c r="E393" s="33"/>
+      <c r="E393" s="33" t="s">
+        <v>888</v>
+      </c>
       <c r="F393" s="32"/>
-      <c r="G393" s="32"/>
+      <c r="G393" s="25">
+        <v>4361370</v>
+      </c>
       <c r="H393" s="32"/>
     </row>
-    <row r="394" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="32"/>
-      <c r="B394" s="32"/>
-      <c r="C394" s="32"/>
+    <row r="394" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="25">
+        <v>4361370</v>
+      </c>
+      <c r="B394" s="32">
+        <v>0</v>
+      </c>
+      <c r="C394" s="32" t="s">
+        <v>860</v>
+      </c>
       <c r="D394" s="32"/>
-      <c r="E394" s="33"/>
+      <c r="E394" s="33" t="s">
+        <v>890</v>
+      </c>
       <c r="F394" s="32"/>
-      <c r="G394" s="32"/>
+      <c r="G394" s="25">
+        <v>4361380</v>
+      </c>
       <c r="H394" s="32"/>
     </row>
-    <row r="395" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="32"/>
-      <c r="B395" s="32"/>
+    <row r="395" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="25">
+        <v>4361380</v>
+      </c>
+      <c r="B395" s="32">
+        <v>2</v>
+      </c>
       <c r="C395" s="32"/>
       <c r="D395" s="32"/>
-      <c r="E395" s="33"/>
+      <c r="E395" s="36" t="s">
+        <v>877</v>
+      </c>
       <c r="F395" s="32"/>
-      <c r="G395" s="32"/>
-      <c r="H395" s="32"/>
-    </row>
-    <row r="396" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="32"/>
-      <c r="B396" s="32"/>
-      <c r="C396" s="32"/>
+      <c r="G395" s="25">
+        <v>4361640</v>
+      </c>
+      <c r="H395" s="32">
+        <v>43602</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="25">
+        <v>4361410</v>
+      </c>
+      <c r="B396" s="32">
+        <v>0</v>
+      </c>
+      <c r="C396" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D396" s="32"/>
-      <c r="E396" s="33"/>
+      <c r="E396" s="33" t="s">
+        <v>901</v>
+      </c>
       <c r="F396" s="32"/>
-      <c r="G396" s="32"/>
+      <c r="G396" s="25">
+        <v>4361420</v>
+      </c>
       <c r="H396" s="32"/>
     </row>
-    <row r="397" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="32"/>
-      <c r="B397" s="32"/>
+    <row r="397" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="25">
+        <v>4361420</v>
+      </c>
+      <c r="B397" s="32">
+        <v>1</v>
+      </c>
       <c r="C397" s="32"/>
       <c r="D397" s="32"/>
-      <c r="E397" s="33"/>
+      <c r="E397" s="33" t="s">
+        <v>902</v>
+      </c>
       <c r="F397" s="32"/>
-      <c r="G397" s="32"/>
+      <c r="G397" s="25">
+        <v>4361430</v>
+      </c>
       <c r="H397" s="32"/>
     </row>
-    <row r="398" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="32"/>
-      <c r="B398" s="32"/>
-      <c r="C398" s="32"/>
+    <row r="398" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="25">
+        <v>4361430</v>
+      </c>
+      <c r="B398" s="32">
+        <v>0</v>
+      </c>
+      <c r="C398" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D398" s="32"/>
-      <c r="E398" s="33"/>
+      <c r="E398" s="33" t="s">
+        <v>903</v>
+      </c>
       <c r="F398" s="32"/>
-      <c r="G398" s="32"/>
+      <c r="G398" s="25">
+        <v>4361440</v>
+      </c>
       <c r="H398" s="32"/>
     </row>
-    <row r="399" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="32"/>
-      <c r="B399" s="32"/>
-      <c r="C399" s="32"/>
-      <c r="D399" s="32"/>
-      <c r="E399" s="33"/>
+    <row r="399" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="25">
+        <v>4361440</v>
+      </c>
+      <c r="B399" s="32">
+        <v>0</v>
+      </c>
+      <c r="C399" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="E399" s="36" t="s">
+        <v>904</v>
+      </c>
       <c r="F399" s="32"/>
-      <c r="G399" s="32"/>
+      <c r="G399" s="25">
+        <v>4361450</v>
+      </c>
       <c r="H399" s="32"/>
     </row>
-    <row r="400" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="32"/>
-      <c r="B400" s="32"/>
-      <c r="C400" s="32"/>
-      <c r="D400" s="32"/>
-      <c r="E400" s="33"/>
+    <row r="400" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="25">
+        <v>4361450</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400" s="35" t="s">
+        <v>868</v>
+      </c>
+      <c r="E400" s="35" t="s">
+        <v>897</v>
+      </c>
       <c r="F400" s="32"/>
-      <c r="G400" s="32"/>
+      <c r="G400" s="25">
+        <v>4361460</v>
+      </c>
       <c r="H400" s="32"/>
     </row>
     <row r="401" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="32"/>
-      <c r="B401" s="32"/>
-      <c r="C401" s="32"/>
-      <c r="D401" s="32"/>
-      <c r="E401" s="33"/>
+      <c r="A401" s="25">
+        <v>4361460</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401" s="35" t="s">
+        <v>863</v>
+      </c>
+      <c r="E401" s="35" t="s">
+        <v>898</v>
+      </c>
       <c r="F401" s="32"/>
-      <c r="G401" s="32"/>
+      <c r="G401" s="25">
+        <v>4361470</v>
+      </c>
       <c r="H401" s="32"/>
     </row>
     <row r="402" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="32"/>
-      <c r="B402" s="32"/>
-      <c r="C402" s="32"/>
-      <c r="D402" s="32"/>
-      <c r="E402" s="33"/>
+      <c r="A402" s="25">
+        <v>4361470</v>
+      </c>
+      <c r="B402" s="69">
+        <v>0</v>
+      </c>
+      <c r="C402" s="70" t="s">
+        <v>868</v>
+      </c>
+      <c r="E402" s="36" t="s">
+        <v>899</v>
+      </c>
       <c r="F402" s="32"/>
-      <c r="G402" s="32"/>
+      <c r="G402" s="25">
+        <v>4361480</v>
+      </c>
       <c r="H402" s="32"/>
     </row>
     <row r="403" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="32"/>
-      <c r="B403" s="32"/>
-      <c r="C403" s="32"/>
-      <c r="D403" s="32"/>
-      <c r="E403" s="33"/>
+      <c r="A403" s="25">
+        <v>4361480</v>
+      </c>
+      <c r="B403" s="69">
+        <v>1</v>
+      </c>
+      <c r="C403" s="71"/>
+      <c r="E403" s="36" t="s">
+        <v>900</v>
+      </c>
       <c r="F403" s="32"/>
-      <c r="G403" s="32"/>
+      <c r="G403" s="25">
+        <v>4361490</v>
+      </c>
       <c r="H403" s="32"/>
     </row>
     <row r="404" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="32"/>
-      <c r="B404" s="32"/>
-      <c r="C404" s="32"/>
-      <c r="D404" s="32"/>
-      <c r="E404" s="33"/>
+      <c r="A404" s="25">
+        <v>4361490</v>
+      </c>
+      <c r="B404" s="32">
+        <v>0</v>
+      </c>
+      <c r="C404" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="E404" s="35" t="s">
+        <v>893</v>
+      </c>
       <c r="F404" s="32"/>
-      <c r="G404" s="32"/>
+      <c r="G404" s="25">
+        <v>4361500</v>
+      </c>
       <c r="H404" s="32"/>
     </row>
     <row r="405" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="32"/>
-      <c r="B405" s="32"/>
-      <c r="C405" s="32"/>
-      <c r="D405" s="32"/>
-      <c r="E405" s="33"/>
+      <c r="A405" s="25">
+        <v>4361500</v>
+      </c>
+      <c r="B405" s="71">
+        <v>0</v>
+      </c>
+      <c r="C405" s="70" t="s">
+        <v>868</v>
+      </c>
+      <c r="E405" s="35" t="s">
+        <v>892</v>
+      </c>
       <c r="F405" s="32"/>
-      <c r="G405" s="32"/>
+      <c r="G405" s="25">
+        <v>4361510</v>
+      </c>
       <c r="H405" s="32"/>
     </row>
     <row r="406" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="32"/>
-      <c r="B406" s="32"/>
-      <c r="C406" s="32"/>
-      <c r="D406" s="32"/>
-      <c r="E406" s="33"/>
+      <c r="A406" s="25">
+        <v>4361510</v>
+      </c>
+      <c r="B406" s="32">
+        <v>0</v>
+      </c>
+      <c r="C406" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="E406" s="57" t="s">
+        <v>895</v>
+      </c>
       <c r="F406" s="32"/>
-      <c r="G406" s="32"/>
+      <c r="G406" s="25">
+        <v>4361520</v>
+      </c>
       <c r="H406" s="32"/>
     </row>
     <row r="407" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="32"/>
-      <c r="B407" s="32"/>
-      <c r="C407" s="32"/>
+      <c r="A407" s="25">
+        <v>4361520</v>
+      </c>
+      <c r="B407" s="32">
+        <v>0</v>
+      </c>
+      <c r="C407" s="32" t="s">
+        <v>866</v>
+      </c>
       <c r="D407" s="32"/>
-      <c r="E407" s="33"/>
+      <c r="E407" s="33" t="s">
+        <v>894</v>
+      </c>
       <c r="F407" s="32"/>
-      <c r="G407" s="32"/>
+      <c r="G407" s="25">
+        <v>4361530</v>
+      </c>
       <c r="H407" s="32"/>
     </row>
     <row r="408" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="32"/>
-      <c r="B408" s="32"/>
-      <c r="C408" s="32"/>
-      <c r="D408" s="32"/>
-      <c r="E408" s="33"/>
+      <c r="A408" s="25">
+        <v>4361530</v>
+      </c>
+      <c r="B408" s="50">
+        <v>0</v>
+      </c>
+      <c r="C408" s="70" t="s">
+        <v>863</v>
+      </c>
+      <c r="E408" s="57" t="s">
+        <v>861</v>
+      </c>
       <c r="F408" s="32"/>
-      <c r="G408" s="32"/>
+      <c r="G408" s="25">
+        <v>4361540</v>
+      </c>
       <c r="H408" s="32"/>
     </row>
     <row r="409" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="32"/>
-      <c r="B409" s="32"/>
-      <c r="C409" s="32"/>
-      <c r="D409" s="32"/>
-      <c r="E409" s="33"/>
+      <c r="A409" s="25">
+        <v>4361540</v>
+      </c>
+      <c r="B409" s="71">
+        <v>1</v>
+      </c>
+      <c r="C409" s="71"/>
+      <c r="E409" s="57" t="s">
+        <v>896</v>
+      </c>
       <c r="F409" s="32"/>
-      <c r="G409" s="32"/>
+      <c r="G409" s="25">
+        <v>4361550</v>
+      </c>
       <c r="H409" s="32"/>
     </row>
     <row r="410" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="32"/>
-      <c r="B410" s="32"/>
-      <c r="C410" s="32"/>
+      <c r="A410" s="25">
+        <v>4361550</v>
+      </c>
+      <c r="B410" s="32">
+        <v>0</v>
+      </c>
+      <c r="C410" s="32" t="s">
+        <v>863</v>
+      </c>
       <c r="D410" s="32"/>
-      <c r="E410" s="33"/>
+      <c r="E410" s="33" t="s">
+        <v>891</v>
+      </c>
       <c r="F410" s="32"/>
-      <c r="G410" s="32"/>
+      <c r="G410" s="25">
+        <v>4361560</v>
+      </c>
       <c r="H410" s="32"/>
     </row>
     <row r="411" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="32"/>
-      <c r="B411" s="32"/>
-      <c r="C411" s="32"/>
+      <c r="A411" s="25">
+        <v>4361560</v>
+      </c>
+      <c r="B411" s="32">
+        <v>0</v>
+      </c>
+      <c r="C411" s="32" t="s">
+        <v>860</v>
+      </c>
       <c r="D411" s="32"/>
-      <c r="E411" s="33"/>
+      <c r="E411" s="33" t="s">
+        <v>905</v>
+      </c>
       <c r="F411" s="32"/>
-      <c r="G411" s="32"/>
+      <c r="G411" s="25">
+        <v>4361570</v>
+      </c>
       <c r="H411" s="32"/>
     </row>
     <row r="412" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="32"/>
-      <c r="B412" s="32"/>
+      <c r="A412" s="25">
+        <v>4361570</v>
+      </c>
+      <c r="B412" s="32">
+        <v>2</v>
+      </c>
       <c r="C412" s="32"/>
       <c r="D412" s="32"/>
-      <c r="E412" s="33"/>
+      <c r="E412" s="36" t="s">
+        <v>877</v>
+      </c>
       <c r="F412" s="32"/>
-      <c r="G412" s="32"/>
-      <c r="H412" s="32"/>
+      <c r="G412" s="25">
+        <v>4361640</v>
+      </c>
+      <c r="H412" s="32">
+        <v>43602</v>
+      </c>
     </row>
     <row r="413" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="32"/>
-      <c r="B413" s="32"/>
-      <c r="C413" s="32"/>
-      <c r="D413" s="32"/>
-      <c r="E413" s="33"/>
-      <c r="F413" s="32"/>
-      <c r="G413" s="32"/>
+      <c r="A413" s="68">
+        <v>4361610</v>
+      </c>
+      <c r="B413" s="50">
+        <v>0</v>
+      </c>
+      <c r="C413" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="E413" s="57" t="s">
+        <v>917</v>
+      </c>
+      <c r="G413" s="68">
+        <v>4361620</v>
+      </c>
       <c r="H413" s="32"/>
     </row>
     <row r="414" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="32"/>
-      <c r="B414" s="32"/>
-      <c r="C414" s="32"/>
-      <c r="D414" s="32"/>
-      <c r="E414" s="33"/>
-      <c r="F414" s="32"/>
-      <c r="G414" s="32"/>
+      <c r="A414" s="68">
+        <v>4361620</v>
+      </c>
+      <c r="B414" s="50">
+        <v>1</v>
+      </c>
+      <c r="E414" s="57" t="s">
+        <v>918</v>
+      </c>
+      <c r="G414" s="68">
+        <v>4361630</v>
+      </c>
       <c r="H414" s="32"/>
     </row>
     <row r="415" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="32"/>
-      <c r="B415" s="32"/>
-      <c r="C415" s="32"/>
-      <c r="D415" s="32"/>
-      <c r="E415" s="33"/>
+      <c r="A415" s="68">
+        <v>4361630</v>
+      </c>
+      <c r="B415" s="72">
+        <v>2</v>
+      </c>
+      <c r="E415" s="36" t="s">
+        <v>877</v>
+      </c>
       <c r="F415" s="32"/>
-      <c r="G415" s="32"/>
-      <c r="H415" s="32"/>
+      <c r="G415" s="25">
+        <v>4361640</v>
+      </c>
+      <c r="H415" s="32">
+        <v>43602</v>
+      </c>
     </row>
     <row r="416" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="32"/>
-      <c r="B416" s="32"/>
-      <c r="C416" s="32"/>
-      <c r="D416" s="32"/>
-      <c r="E416" s="33"/>
+      <c r="A416" s="25">
+        <v>4361640</v>
+      </c>
+      <c r="B416" s="50">
+        <v>2</v>
+      </c>
+      <c r="E416" s="57" t="s">
+        <v>906</v>
+      </c>
       <c r="F416" s="32"/>
       <c r="G416" s="32"/>
-      <c r="H416" s="32"/>
+      <c r="H416" s="32">
+        <v>43603</v>
+      </c>
     </row>
     <row r="417" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="32"/>
-      <c r="B417" s="32"/>
-      <c r="C417" s="32"/>
-      <c r="D417" s="32"/>
-      <c r="E417" s="33"/>
+      <c r="A417" s="73">
+        <v>4362010</v>
+      </c>
+      <c r="B417" s="50">
+        <v>0</v>
+      </c>
+      <c r="C417" s="35" t="s">
+        <v>863</v>
+      </c>
+      <c r="E417" s="57" t="s">
+        <v>911</v>
+      </c>
       <c r="F417" s="32"/>
-      <c r="G417" s="32"/>
+      <c r="G417" s="32">
+        <v>4362020</v>
+      </c>
       <c r="H417" s="32"/>
     </row>
     <row r="418" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="32"/>
-      <c r="B418" s="32"/>
-      <c r="C418" s="32"/>
-      <c r="D418" s="32"/>
-      <c r="E418" s="33"/>
+      <c r="A418" s="32">
+        <v>4362020</v>
+      </c>
+      <c r="B418" s="72">
+        <v>0</v>
+      </c>
+      <c r="C418" s="72" t="s">
+        <v>862</v>
+      </c>
+      <c r="E418" s="57" t="s">
+        <v>909</v>
+      </c>
       <c r="F418" s="32"/>
-      <c r="G418" s="32"/>
+      <c r="G418" s="32">
+        <v>4362030</v>
+      </c>
       <c r="H418" s="32"/>
     </row>
     <row r="419" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="32"/>
-      <c r="B419" s="32"/>
-      <c r="C419" s="32"/>
-      <c r="D419" s="32"/>
-      <c r="E419" s="33"/>
+      <c r="A419" s="32">
+        <v>4362030</v>
+      </c>
+      <c r="B419" s="72">
+        <v>1</v>
+      </c>
+      <c r="E419" s="57" t="s">
+        <v>910</v>
+      </c>
       <c r="F419" s="32"/>
-      <c r="G419" s="32"/>
+      <c r="G419" s="32">
+        <v>4362040</v>
+      </c>
       <c r="H419" s="32"/>
     </row>
     <row r="420" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="32"/>
-      <c r="B420" s="32"/>
-      <c r="C420" s="32"/>
-      <c r="D420" s="32"/>
-      <c r="E420" s="33"/>
+      <c r="A420" s="32">
+        <v>4362040</v>
+      </c>
+      <c r="B420" s="72">
+        <v>2</v>
+      </c>
+      <c r="E420" s="57" t="s">
+        <v>913</v>
+      </c>
       <c r="F420" s="32"/>
       <c r="G420" s="32"/>
-      <c r="H420" s="32"/>
+      <c r="H420" s="51">
+        <v>43604</v>
+      </c>
     </row>
     <row r="421" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="32"/>
-      <c r="B421" s="32"/>
-      <c r="C421" s="32"/>
-      <c r="D421" s="32"/>
-      <c r="E421" s="33"/>
+      <c r="A421" s="32">
+        <v>4362110</v>
+      </c>
+      <c r="B421" s="50">
+        <v>0</v>
+      </c>
+      <c r="C421" s="35" t="s">
+        <v>863</v>
+      </c>
+      <c r="E421" s="57" t="s">
+        <v>912</v>
+      </c>
       <c r="F421" s="32"/>
-      <c r="G421" s="32"/>
+      <c r="G421" s="32">
+        <v>4362120</v>
+      </c>
       <c r="H421" s="32"/>
     </row>
     <row r="422" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="32"/>
-      <c r="B422" s="32"/>
-      <c r="C422" s="32"/>
-      <c r="D422" s="32"/>
-      <c r="E422" s="33"/>
+      <c r="A422" s="32">
+        <v>4362120</v>
+      </c>
+      <c r="B422" s="50">
+        <v>1</v>
+      </c>
+      <c r="E422" s="57" t="s">
+        <v>919</v>
+      </c>
       <c r="F422" s="32"/>
-      <c r="G422" s="32"/>
+      <c r="G422" s="32">
+        <v>4362130</v>
+      </c>
       <c r="H422" s="32"/>
     </row>
     <row r="423" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="32"/>
-      <c r="B423" s="32"/>
+      <c r="A423" s="32">
+        <v>4362130</v>
+      </c>
+      <c r="B423" s="32">
+        <v>1</v>
+      </c>
       <c r="C423" s="32"/>
       <c r="D423" s="32"/>
-      <c r="E423" s="33"/>
+      <c r="E423" s="33" t="s">
+        <v>914</v>
+      </c>
       <c r="F423" s="32"/>
-      <c r="G423" s="32"/>
+      <c r="G423" s="32">
+        <v>4362140</v>
+      </c>
       <c r="H423" s="32"/>
     </row>
     <row r="424" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="32"/>
-      <c r="B424" s="32"/>
+      <c r="A424" s="32">
+        <v>4362140</v>
+      </c>
+      <c r="B424" s="32">
+        <v>2</v>
+      </c>
       <c r="C424" s="32"/>
       <c r="D424" s="32"/>
-      <c r="E424" s="33"/>
+      <c r="E424" s="33" t="s">
+        <v>920</v>
+      </c>
       <c r="F424" s="32"/>
       <c r="G424" s="32"/>
       <c r="H424" s="32"/>
     </row>
     <row r="425" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="32"/>
-      <c r="B425" s="32"/>
-      <c r="C425" s="32"/>
+      <c r="A425" s="73">
+        <v>4363010</v>
+      </c>
+      <c r="B425" s="32">
+        <v>0</v>
+      </c>
+      <c r="C425" s="35" t="s">
+        <v>863</v>
+      </c>
       <c r="D425" s="32"/>
-      <c r="E425" s="33"/>
+      <c r="E425" s="33" t="s">
+        <v>925</v>
+      </c>
       <c r="F425" s="32"/>
-      <c r="G425" s="32"/>
+      <c r="G425" s="32">
+        <v>4363020</v>
+      </c>
       <c r="H425" s="32"/>
     </row>
     <row r="426" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="32"/>
-      <c r="B426" s="32"/>
+      <c r="A426" s="32">
+        <v>4363020</v>
+      </c>
+      <c r="B426" s="32">
+        <v>2</v>
+      </c>
       <c r="C426" s="32"/>
       <c r="D426" s="32"/>
-      <c r="E426" s="33"/>
+      <c r="E426" s="33" t="s">
+        <v>926</v>
+      </c>
       <c r="F426" s="32"/>
-      <c r="G426" s="32"/>
+      <c r="G426" s="32">
+        <v>4363030</v>
+      </c>
       <c r="H426" s="32"/>
     </row>
     <row r="427" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="32"/>
-      <c r="B427" s="32"/>
+      <c r="A427" s="32">
+        <v>4363030</v>
+      </c>
+      <c r="B427" s="32">
+        <v>1</v>
+      </c>
       <c r="C427" s="32"/>
       <c r="D427" s="32"/>
-      <c r="E427" s="33"/>
+      <c r="E427" s="33" t="s">
+        <v>924</v>
+      </c>
       <c r="F427" s="32"/>
       <c r="G427" s="32"/>
       <c r="H427" s="32"/>
@@ -15295,49 +16199,10 @@
       <c r="G670" s="32"/>
       <c r="H670" s="32"/>
     </row>
-    <row r="671" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A671" s="32"/>
-      <c r="B671" s="32"/>
-      <c r="C671" s="32"/>
-      <c r="D671" s="32"/>
-      <c r="E671" s="33"/>
-      <c r="F671" s="32"/>
-      <c r="G671" s="32"/>
-      <c r="H671" s="32"/>
-    </row>
-    <row r="672" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A672" s="32"/>
-      <c r="B672" s="32"/>
-      <c r="C672" s="32"/>
-      <c r="D672" s="32"/>
-      <c r="E672" s="33"/>
-      <c r="F672" s="32"/>
-      <c r="G672" s="32"/>
-      <c r="H672" s="32"/>
-    </row>
-    <row r="673" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A673" s="32"/>
-      <c r="B673" s="32"/>
-      <c r="C673" s="32"/>
-      <c r="D673" s="32"/>
-      <c r="E673" s="33"/>
-      <c r="F673" s="32"/>
-      <c r="G673" s="32"/>
-      <c r="H673" s="32"/>
-    </row>
-    <row r="674" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A674" s="32"/>
-      <c r="B674" s="32"/>
-      <c r="C674" s="32"/>
-      <c r="D674" s="32"/>
-      <c r="E674" s="33"/>
-      <c r="F674" s="32"/>
-      <c r="G674" s="32"/>
-      <c r="H674" s="32"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15387,13 +16252,13 @@
         <v>40200</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E2" s="33"/>
       <c r="F2" s="32">
@@ -15401,7 +16266,7 @@
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15419,7 +16284,7 @@
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15432,16 +16297,16 @@
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
       <c r="E4" s="33" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F4" s="32">
         <v>4020180</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>563</v>
+        <v>852</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15454,16 +16319,16 @@
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F5" s="32">
         <v>4020250</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>566</v>
+        <v>858</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15471,21 +16336,21 @@
         <v>40202</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E6" s="33"/>
       <c r="F6" s="32"/>
       <c r="G6" s="32" t="s">
-        <v>569</v>
+        <v>851</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15493,21 +16358,21 @@
         <v>40202</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15515,13 +16380,13 @@
         <v>40203</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E8" s="33"/>
       <c r="F8" s="32">
@@ -15529,7 +16394,7 @@
       </c>
       <c r="G8" s="32"/>
       <c r="H8" s="32" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15537,13 +16402,13 @@
         <v>40203</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E9" s="33"/>
       <c r="F9" s="32">
@@ -15551,7 +16416,7 @@
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -15559,13 +16424,13 @@
         <v>40301</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E10" s="33"/>
       <c r="F10" s="32">
@@ -15573,7 +16438,7 @@
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15581,13 +16446,13 @@
         <v>40301</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E11" s="33"/>
       <c r="F11" s="32">
@@ -15595,7 +16460,7 @@
       </c>
       <c r="G11" s="32"/>
       <c r="H11" s="32" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15610,10 +16475,10 @@
       <c r="E12" s="33"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15621,13 +16486,13 @@
         <v>40401</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E13" s="33"/>
       <c r="F13" s="32">
@@ -15635,7 +16500,7 @@
       </c>
       <c r="G13" s="32"/>
       <c r="H13" s="32" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15643,13 +16508,13 @@
         <v>40401</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E14" s="33"/>
       <c r="F14" s="32">
@@ -15657,7 +16522,7 @@
       </c>
       <c r="G14" s="32"/>
       <c r="H14" s="32" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15665,21 +16530,21 @@
         <v>40402</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15694,10 +16559,10 @@
       <c r="E16" s="33"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32" t="s">
-        <v>588</v>
+        <v>850</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15705,13 +16570,13 @@
         <v>40501</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E17" s="33"/>
       <c r="F17" s="32">
@@ -15719,7 +16584,7 @@
       </c>
       <c r="G17" s="32"/>
       <c r="H17" s="32" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15727,13 +16592,13 @@
         <v>40501</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="32">
@@ -15741,7 +16606,7 @@
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="32" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15749,21 +16614,21 @@
         <v>40502</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15771,21 +16636,21 @@
         <v>40502</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15793,13 +16658,13 @@
         <v>40503</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="32">
@@ -15807,7 +16672,7 @@
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="32" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15815,13 +16680,13 @@
         <v>40503</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E22" s="33"/>
       <c r="F22" s="32">
@@ -15829,7 +16694,7 @@
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="32" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15837,13 +16702,13 @@
         <v>40600</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E23" s="33"/>
       <c r="F23" s="32">
@@ -15851,7 +16716,7 @@
       </c>
       <c r="G23" s="32"/>
       <c r="H23" s="32" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15869,7 +16734,7 @@
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="32" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15884,10 +16749,10 @@
       <c r="E25" s="33"/>
       <c r="F25" s="32"/>
       <c r="G25" s="32" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15895,13 +16760,13 @@
         <v>40602</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E26" s="33"/>
       <c r="F26" s="32">
@@ -15909,7 +16774,7 @@
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15917,13 +16782,13 @@
         <v>40602</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E27" s="33"/>
       <c r="F27" s="32">
@@ -15931,7 +16796,7 @@
       </c>
       <c r="G27" s="32"/>
       <c r="H27" s="32" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="82.5" x14ac:dyDescent="0.3">
@@ -15946,10 +16811,10 @@
       <c r="E28" s="33"/>
       <c r="F28" s="32"/>
       <c r="G28" s="32" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15957,21 +16822,21 @@
         <v>40801</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="32"/>
       <c r="G29" s="32" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -15986,10 +16851,10 @@
       <c r="E30" s="33"/>
       <c r="F30" s="32"/>
       <c r="G30" s="32" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16004,10 +16869,10 @@
       <c r="E31" s="33"/>
       <c r="F31" s="32"/>
       <c r="G31" s="32" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16015,13 +16880,13 @@
         <v>40902</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E32" s="33"/>
       <c r="F32" s="32">
@@ -16029,7 +16894,7 @@
       </c>
       <c r="G32" s="32"/>
       <c r="H32" s="32" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16037,13 +16902,13 @@
         <v>40902</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E33" s="33"/>
       <c r="F33" s="32">
@@ -16051,7 +16916,7 @@
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="32" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16059,13 +16924,13 @@
         <v>41000</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E34" s="33"/>
       <c r="F34" s="32">
@@ -16073,7 +16938,7 @@
       </c>
       <c r="G34" s="32"/>
       <c r="H34" s="32" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16091,7 +16956,7 @@
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="32" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16106,10 +16971,10 @@
       <c r="E36" s="33"/>
       <c r="F36" s="32"/>
       <c r="G36" s="32" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16117,13 +16982,13 @@
         <v>41002</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E37" s="33"/>
       <c r="F37" s="32">
@@ -16131,7 +16996,7 @@
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="32" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16139,13 +17004,13 @@
         <v>41002</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E38" s="33"/>
       <c r="F38" s="32">
@@ -16153,7 +17018,7 @@
       </c>
       <c r="G38" s="32"/>
       <c r="H38" s="32" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16168,10 +17033,10 @@
       <c r="E39" s="33"/>
       <c r="F39" s="32"/>
       <c r="G39" s="32" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16179,21 +17044,21 @@
         <v>41201</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E40" s="33"/>
       <c r="F40" s="32"/>
       <c r="G40" s="32" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16208,10 +17073,10 @@
       <c r="E41" s="33"/>
       <c r="F41" s="32"/>
       <c r="G41" s="32" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -16226,10 +17091,10 @@
       <c r="E42" s="33"/>
       <c r="F42" s="32"/>
       <c r="G42" s="32" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16237,13 +17102,13 @@
         <v>41302</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E43" s="33"/>
       <c r="F43" s="32">
@@ -16251,7 +17116,7 @@
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="32" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16259,13 +17124,13 @@
         <v>41302</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E44" s="33"/>
       <c r="F44" s="32">
@@ -16273,7 +17138,7 @@
       </c>
       <c r="G44" s="32"/>
       <c r="H44" s="32" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16281,13 +17146,13 @@
         <v>41400</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E45" s="33"/>
       <c r="F45" s="32">
@@ -16295,7 +17160,7 @@
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="32" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16313,7 +17178,7 @@
       </c>
       <c r="G46" s="32"/>
       <c r="H46" s="32" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16321,13 +17186,13 @@
         <v>41401</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E47" s="33"/>
       <c r="F47" s="32">
@@ -16335,7 +17200,7 @@
       </c>
       <c r="G47" s="32"/>
       <c r="H47" s="32" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16343,13 +17208,13 @@
         <v>41401</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E48" s="33"/>
       <c r="F48" s="32">
@@ -16357,7 +17222,7 @@
       </c>
       <c r="G48" s="32"/>
       <c r="H48" s="32" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16375,7 +17240,7 @@
       </c>
       <c r="G49" s="32"/>
       <c r="H49" s="32" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16390,10 +17255,10 @@
       <c r="E50" s="33"/>
       <c r="F50" s="32"/>
       <c r="G50" s="32" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16408,10 +17273,10 @@
       <c r="E51" s="33"/>
       <c r="F51" s="32"/>
       <c r="G51" s="32" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16426,10 +17291,10 @@
       <c r="E52" s="33"/>
       <c r="F52" s="32"/>
       <c r="G52" s="32" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16437,13 +17302,13 @@
         <v>41490</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C53" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D53" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E53" s="33"/>
       <c r="F53" s="32">
@@ -16451,7 +17316,7 @@
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="32" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16459,13 +17324,13 @@
         <v>41490</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C54" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D54" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E54" s="33"/>
       <c r="F54" s="32">
@@ -16473,7 +17338,7 @@
       </c>
       <c r="G54" s="32"/>
       <c r="H54" s="32" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16481,13 +17346,13 @@
         <v>41501</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D55" s="33" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E55" s="33"/>
       <c r="F55" s="32">
@@ -16495,7 +17360,7 @@
       </c>
       <c r="G55" s="32"/>
       <c r="H55" s="32" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16503,13 +17368,13 @@
         <v>41501</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E56" s="33"/>
       <c r="F56" s="32">
@@ -16517,7 +17382,7 @@
       </c>
       <c r="G56" s="32"/>
       <c r="H56" s="32" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16535,7 +17400,7 @@
       </c>
       <c r="G57" s="32"/>
       <c r="H57" s="32" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16550,10 +17415,10 @@
       <c r="E58" s="33"/>
       <c r="F58" s="32"/>
       <c r="G58" s="32" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16561,13 +17426,13 @@
         <v>41601</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C59" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D59" s="33" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E59" s="33"/>
       <c r="F59" s="32">
@@ -16575,7 +17440,7 @@
       </c>
       <c r="G59" s="32"/>
       <c r="H59" s="32" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16583,13 +17448,13 @@
         <v>41601</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C60" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D60" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E60" s="33"/>
       <c r="F60" s="32">
@@ -16597,7 +17462,7 @@
       </c>
       <c r="G60" s="32"/>
       <c r="H60" s="32" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16615,7 +17480,7 @@
       </c>
       <c r="G61" s="32"/>
       <c r="H61" s="32" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16623,21 +17488,21 @@
         <v>41690</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C62" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D62" s="33" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="E62" s="33"/>
       <c r="F62" s="32"/>
       <c r="G62" s="32" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="H62" s="32" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16652,10 +17517,10 @@
       <c r="E63" s="33"/>
       <c r="F63" s="32"/>
       <c r="G63" s="32" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="H63" s="32" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16663,13 +17528,13 @@
         <v>41701</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C64" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D64" s="33" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E64" s="33"/>
       <c r="F64" s="32">
@@ -16677,7 +17542,7 @@
       </c>
       <c r="G64" s="32"/>
       <c r="H64" s="32" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16685,13 +17550,13 @@
         <v>41701</v>
       </c>
       <c r="B65" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C65" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D65" s="33" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E65" s="33"/>
       <c r="F65" s="32">
@@ -16699,7 +17564,7 @@
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="32" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16717,7 +17582,7 @@
       </c>
       <c r="G66" s="32"/>
       <c r="H66" s="32" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16732,10 +17597,10 @@
       <c r="E67" s="33"/>
       <c r="F67" s="32"/>
       <c r="G67" s="32" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="H67" s="32" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16750,10 +17615,10 @@
       <c r="E68" s="33"/>
       <c r="F68" s="32"/>
       <c r="G68" s="32" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="H68" s="32" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16768,10 +17633,10 @@
       <c r="E69" s="33"/>
       <c r="F69" s="32"/>
       <c r="G69" s="32" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="H69" s="32" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16779,13 +17644,13 @@
         <v>41790</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D70" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E70" s="33"/>
       <c r="F70" s="32">
@@ -16793,7 +17658,7 @@
       </c>
       <c r="G70" s="32"/>
       <c r="H70" s="32" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16801,13 +17666,13 @@
         <v>41790</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E71" s="33"/>
       <c r="F71" s="32">
@@ -16815,7 +17680,7 @@
       </c>
       <c r="G71" s="32"/>
       <c r="H71" s="32" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16823,13 +17688,13 @@
         <v>41800</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C72" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E72" s="33"/>
       <c r="F72" s="32">
@@ -16837,7 +17702,7 @@
       </c>
       <c r="G72" s="32"/>
       <c r="H72" s="32" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16855,7 +17720,7 @@
       </c>
       <c r="G73" s="32"/>
       <c r="H73" s="32" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16863,13 +17728,13 @@
         <v>41801</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C74" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E74" s="33"/>
       <c r="F74" s="32">
@@ -16877,7 +17742,7 @@
       </c>
       <c r="G74" s="32"/>
       <c r="H74" s="32" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16895,7 +17760,7 @@
       </c>
       <c r="G75" s="32"/>
       <c r="H75" s="32" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16910,10 +17775,10 @@
       <c r="E76" s="33"/>
       <c r="F76" s="32"/>
       <c r="G76" s="32" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="H76" s="32" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16928,10 +17793,10 @@
       <c r="E77" s="33"/>
       <c r="F77" s="32"/>
       <c r="G77" s="32" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="H77" s="32" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16939,13 +17804,13 @@
         <v>41890</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E78" s="33"/>
       <c r="F78" s="32">
@@ -16953,7 +17818,7 @@
       </c>
       <c r="G78" s="32"/>
       <c r="H78" s="32" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16961,13 +17826,13 @@
         <v>41890</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="32">
@@ -16975,7 +17840,7 @@
       </c>
       <c r="G79" s="32"/>
       <c r="H79" s="32" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16983,13 +17848,13 @@
         <v>41901</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C80" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D80" s="33" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E80" s="33"/>
       <c r="F80" s="32">
@@ -16997,7 +17862,7 @@
       </c>
       <c r="G80" s="32"/>
       <c r="H80" s="32" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17015,7 +17880,7 @@
       </c>
       <c r="G81" s="32"/>
       <c r="H81" s="32" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17030,10 +17895,10 @@
       <c r="E82" s="33"/>
       <c r="F82" s="32"/>
       <c r="G82" s="32" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="H82" s="32" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17041,13 +17906,13 @@
         <v>42001</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E83" s="33"/>
       <c r="F83" s="32">
@@ -17055,7 +17920,7 @@
       </c>
       <c r="G83" s="32"/>
       <c r="H83" s="32" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17073,7 +17938,7 @@
       </c>
       <c r="G84" s="32"/>
       <c r="H84" s="32" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17081,21 +17946,21 @@
         <v>42090</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E85" s="33"/>
       <c r="F85" s="32"/>
       <c r="G85" s="32" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="H85" s="32" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17110,10 +17975,10 @@
       <c r="E86" s="33"/>
       <c r="F86" s="32"/>
       <c r="G86" s="32" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="H86" s="32" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17121,13 +17986,13 @@
         <v>42101</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C87" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D87" s="33" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E87" s="33"/>
       <c r="F87" s="32">
@@ -17135,7 +18000,7 @@
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="32" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17153,7 +18018,7 @@
       </c>
       <c r="G88" s="32"/>
       <c r="H88" s="32" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17168,10 +18033,10 @@
       <c r="E89" s="33"/>
       <c r="F89" s="32"/>
       <c r="G89" s="32" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="H89" s="32" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17186,10 +18051,10 @@
       <c r="E90" s="33"/>
       <c r="F90" s="32"/>
       <c r="G90" s="32" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="H90" s="32" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17197,13 +18062,13 @@
         <v>42190</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C91" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D91" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E91" s="33"/>
       <c r="F91" s="32">
@@ -17211,7 +18076,7 @@
       </c>
       <c r="G91" s="32"/>
       <c r="H91" s="32" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17219,13 +18084,13 @@
         <v>42190</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D92" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E92" s="33"/>
       <c r="F92" s="32">
@@ -17233,7 +18098,7 @@
       </c>
       <c r="G92" s="32"/>
       <c r="H92" s="32" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17241,13 +18106,13 @@
         <v>42200</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D93" s="33" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="E93" s="33"/>
       <c r="F93" s="32">
@@ -17255,7 +18120,7 @@
       </c>
       <c r="G93" s="32"/>
       <c r="H93" s="32" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17273,7 +18138,7 @@
       </c>
       <c r="G94" s="32"/>
       <c r="H94" s="32" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17288,10 +18153,10 @@
       <c r="E95" s="33"/>
       <c r="F95" s="32"/>
       <c r="G95" s="32" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="H95" s="32" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17299,13 +18164,13 @@
         <v>42202</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E96" s="33"/>
       <c r="F96" s="32">
@@ -17313,7 +18178,7 @@
       </c>
       <c r="G96" s="32"/>
       <c r="H96" s="32" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17321,13 +18186,13 @@
         <v>42202</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C97" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D97" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E97" s="33"/>
       <c r="F97" s="32">
@@ -17335,7 +18200,7 @@
       </c>
       <c r="G97" s="32"/>
       <c r="H97" s="32" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17350,10 +18215,10 @@
       <c r="E98" s="33"/>
       <c r="F98" s="32"/>
       <c r="G98" s="32" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="H98" s="32" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17361,21 +18226,21 @@
         <v>42401</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D99" s="33" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="E99" s="33"/>
       <c r="F99" s="32"/>
       <c r="G99" s="32" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="H99" s="32" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17390,10 +18255,10 @@
       <c r="E100" s="33"/>
       <c r="F100" s="32"/>
       <c r="G100" s="32" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="H100" s="32" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17408,10 +18273,10 @@
       <c r="E101" s="33"/>
       <c r="F101" s="32"/>
       <c r="G101" s="32" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="H101" s="32" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17419,13 +18284,13 @@
         <v>42502</v>
       </c>
       <c r="B102" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D102" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E102" s="33"/>
       <c r="F102" s="32">
@@ -17433,7 +18298,7 @@
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="32" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17441,13 +18306,13 @@
         <v>42502</v>
       </c>
       <c r="B103" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C103" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D103" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E103" s="33"/>
       <c r="F103" s="32">
@@ -17455,7 +18320,7 @@
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="32" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -17463,126 +18328,222 @@
         <v>43601</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>666</v>
+        <v>916</v>
       </c>
       <c r="E104" s="33"/>
-      <c r="F104" s="32">
-        <v>4361020</v>
+      <c r="F104" s="72">
+        <v>4361610</v>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="32" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="32">
+        <v>43601</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>854</v>
+      </c>
+      <c r="C105" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="D105" s="33" t="s">
+        <v>849</v>
+      </c>
+      <c r="E105" s="33"/>
+      <c r="F105" s="32">
+        <v>4361020</v>
+      </c>
+      <c r="G105" s="32"/>
+      <c r="H105" s="32" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A106" s="32">
+        <v>43601</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>855</v>
+      </c>
+      <c r="C106" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="D106" s="33" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="32"/>
-      <c r="B105" s="32" t="s">
-        <v>571</v>
-      </c>
-      <c r="C105" s="33"/>
-      <c r="D105" s="33"/>
-      <c r="E105" s="33"/>
-      <c r="F105" s="32"/>
-      <c r="G105" s="32"/>
-      <c r="H105" s="32"/>
-    </row>
-    <row r="106" spans="1:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="32"/>
-      <c r="B106" s="32"/>
-      <c r="C106" s="33"/>
-      <c r="D106" s="33"/>
       <c r="E106" s="33"/>
-      <c r="F106" s="32"/>
+      <c r="F106" s="32">
+        <v>4361210</v>
+      </c>
       <c r="G106" s="32"/>
       <c r="H106" s="32" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="32"/>
-      <c r="B107" s="32"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A107" s="32">
+        <v>43601</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>915</v>
+      </c>
+      <c r="C107" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="D107" s="33" t="s">
+        <v>859</v>
+      </c>
       <c r="E107" s="33"/>
-      <c r="F107" s="32"/>
+      <c r="F107" s="32">
+        <v>4361310</v>
+      </c>
       <c r="G107" s="32"/>
-      <c r="H107" s="32"/>
+      <c r="H107" s="32" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="108" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="32"/>
-      <c r="B108" s="32"/>
+      <c r="A108" s="32">
+        <v>43601</v>
+      </c>
+      <c r="B108" s="32">
+        <v>5</v>
+      </c>
       <c r="C108" s="33"/>
       <c r="D108" s="33"/>
       <c r="E108" s="33"/>
-      <c r="F108" s="32"/>
+      <c r="F108" s="25">
+        <v>4361410</v>
+      </c>
       <c r="G108" s="32"/>
-      <c r="H108" s="32"/>
+      <c r="H108" s="32" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="109" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="32"/>
-      <c r="B109" s="32"/>
+      <c r="A109" s="32">
+        <v>43602</v>
+      </c>
+      <c r="B109" s="32">
+        <v>1</v>
+      </c>
       <c r="C109" s="33"/>
       <c r="D109" s="33"/>
       <c r="E109" s="33"/>
       <c r="F109" s="32"/>
-      <c r="G109" s="32"/>
-      <c r="H109" s="32"/>
+      <c r="G109" s="32" t="s">
+        <v>872</v>
+      </c>
+      <c r="H109" s="32" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="110" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="32"/>
-      <c r="B110" s="32"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="33"/>
+      <c r="A110" s="32">
+        <v>43603</v>
+      </c>
+      <c r="B110" s="32" t="s">
+        <v>554</v>
+      </c>
+      <c r="C110" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="D110" s="33" t="s">
+        <v>570</v>
+      </c>
       <c r="E110" s="33"/>
-      <c r="F110" s="32"/>
+      <c r="F110" s="32">
+        <v>4362010</v>
+      </c>
       <c r="G110" s="32"/>
-      <c r="H110" s="32"/>
+      <c r="H110" s="32" t="s">
+        <v>870</v>
+      </c>
     </row>
     <row r="111" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="32"/>
-      <c r="B111" s="32"/>
-      <c r="C111" s="33"/>
-      <c r="D111" s="33"/>
+      <c r="A111" s="32">
+        <v>43603</v>
+      </c>
+      <c r="B111" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="C111" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="D111" s="33" t="s">
+        <v>572</v>
+      </c>
       <c r="E111" s="33"/>
-      <c r="F111" s="32"/>
-      <c r="G111" s="32"/>
-      <c r="H111" s="32"/>
-    </row>
-    <row r="112" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="32"/>
-      <c r="B112" s="32"/>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="32"/>
-      <c r="G112" s="32"/>
-      <c r="H112" s="32"/>
-    </row>
-    <row r="113" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="32"/>
-      <c r="B113" s="32"/>
-      <c r="C113" s="33"/>
-      <c r="D113" s="33"/>
-      <c r="E113" s="33"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
+      <c r="F111" s="32">
+        <v>4362110</v>
+      </c>
+      <c r="G111" s="33" t="s">
+        <v>931</v>
+      </c>
+      <c r="H111" s="32" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A112" s="51">
+        <v>43604</v>
+      </c>
+      <c r="B112" s="75">
+        <v>1</v>
+      </c>
+      <c r="G112" s="31" t="s">
+        <v>929</v>
+      </c>
+      <c r="H112" s="51" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="75">
+        <v>43605</v>
+      </c>
+      <c r="B113" s="76" t="s">
+        <v>907</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="D113" s="35" t="s">
+        <v>930</v>
+      </c>
+      <c r="F113">
+        <v>4360011</v>
+      </c>
+      <c r="H113" s="72" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="114" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="32"/>
-      <c r="B114" s="32"/>
+      <c r="A114" s="75">
+        <v>43605</v>
+      </c>
+      <c r="B114" s="32">
+        <v>2</v>
+      </c>
       <c r="C114" s="33"/>
       <c r="D114" s="33"/>
       <c r="E114" s="33"/>
-      <c r="F114" s="32"/>
+      <c r="F114" s="32">
+        <v>4363010</v>
+      </c>
       <c r="G114" s="32"/>
-      <c r="H114" s="32"/>
+      <c r="H114" s="32" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="115" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="32"/>
@@ -18047,6 +19008,7 @@
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18101,7 +19063,7 @@
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
       <c r="E2" s="33" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="F2" s="54"/>
       <c r="G2" s="45"/>
@@ -18117,11 +19079,11 @@
         <v>0</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="33" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="F3" s="54"/>
       <c r="G3" s="45">
@@ -18137,11 +19099,11 @@
         <v>0</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="33" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F4" s="54"/>
       <c r="G4" s="45">
@@ -18157,11 +19119,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="33" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="45">
@@ -18177,11 +19139,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D6" s="43"/>
       <c r="E6" s="33" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="45">
@@ -18197,11 +19159,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="56" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="F7" s="54"/>
       <c r="G7" s="45">
@@ -18217,11 +19179,11 @@
         <v>0</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D8" s="45"/>
       <c r="E8" s="59" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="F8" s="60"/>
       <c r="G8" s="61">
@@ -18237,11 +19199,11 @@
         <v>0</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D9" s="45"/>
       <c r="E9" s="46" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="F9" s="45"/>
       <c r="G9" s="45">
@@ -18257,11 +19219,11 @@
         <v>0</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="46" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="F10" s="45"/>
       <c r="G10" s="45">
@@ -18279,7 +19241,7 @@
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
       <c r="E11" s="46" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="45">
@@ -18297,7 +19259,7 @@
       <c r="C12" s="45"/>
       <c r="D12" s="45"/>
       <c r="E12" s="46" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="F12" s="45"/>
       <c r="G12" s="45">
@@ -18336,7 +19298,7 @@
       <c r="C14" s="45"/>
       <c r="D14" s="45"/>
       <c r="E14" s="46" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45">
@@ -18353,11 +19315,11 @@
         <v>0</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D15" s="45"/>
       <c r="E15" s="46" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F15" s="45"/>
       <c r="G15" s="45">
@@ -18373,11 +19335,11 @@
         <v>0</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D16" s="45"/>
       <c r="E16" s="46" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="45">
@@ -18397,7 +19359,7 @@
       </c>
       <c r="D17" s="45"/>
       <c r="E17" s="46" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45"/>
@@ -18413,11 +19375,11 @@
         <v>0</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D18" s="45"/>
       <c r="E18" s="25" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F18" s="45"/>
       <c r="G18" s="45">
@@ -18437,7 +19399,7 @@
       </c>
       <c r="D19" s="45"/>
       <c r="E19" s="46" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="F19" s="45"/>
       <c r="G19" s="45">
@@ -18455,7 +19417,7 @@
       <c r="C20" s="45"/>
       <c r="D20" s="45"/>
       <c r="E20" s="46" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="F20" s="45"/>
       <c r="G20" s="45">
@@ -18471,11 +19433,11 @@
         <v>0</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D21" s="45"/>
       <c r="E21" s="46" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="45">
@@ -18495,7 +19457,7 @@
       </c>
       <c r="D22" s="45"/>
       <c r="E22" s="25" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="F22" s="45"/>
       <c r="G22" s="45">
@@ -18513,7 +19475,7 @@
       <c r="C23" s="45"/>
       <c r="D23" s="45"/>
       <c r="E23" s="46" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F23" s="45"/>
       <c r="G23" s="45">
@@ -18531,7 +19493,7 @@
       <c r="C24" s="45"/>
       <c r="D24" s="45"/>
       <c r="E24" s="46" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F24" s="45"/>
       <c r="G24" s="45">
@@ -18549,7 +19511,7 @@
       <c r="C25" s="45"/>
       <c r="D25" s="45"/>
       <c r="E25" s="25" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
@@ -18565,11 +19527,11 @@
         <v>0</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D26" s="55"/>
       <c r="E26" s="25" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F26" s="45"/>
       <c r="G26" s="45">
@@ -18589,7 +19551,7 @@
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="25" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="F27" s="45"/>
       <c r="G27" s="45">
@@ -18605,11 +19567,11 @@
         <v>0</v>
       </c>
       <c r="C28" s="58" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D28" s="55"/>
       <c r="E28" s="25" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="45">
@@ -18625,11 +19587,11 @@
         <v>0</v>
       </c>
       <c r="C29" s="58" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="25" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F29" s="45"/>
       <c r="G29" s="45">
@@ -18649,7 +19611,7 @@
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="25" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F30" s="45"/>
       <c r="G30" s="45">
@@ -18667,7 +19629,7 @@
       <c r="C31" s="58"/>
       <c r="D31" s="55"/>
       <c r="E31" s="25" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="F31" s="45"/>
       <c r="G31" s="45">
@@ -18685,7 +19647,7 @@
       <c r="C32" s="58"/>
       <c r="D32" s="55"/>
       <c r="E32" s="25" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="F32" s="45"/>
       <c r="G32" s="45">
@@ -18703,7 +19665,7 @@
       <c r="C33" s="58"/>
       <c r="D33" s="55"/>
       <c r="E33" s="25" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F33" s="45"/>
       <c r="G33" s="45">
@@ -18721,7 +19683,7 @@
       <c r="C34" s="55"/>
       <c r="D34" s="55"/>
       <c r="E34" s="25" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F34" s="45"/>
       <c r="G34" s="45"/>
@@ -18739,7 +19701,7 @@
       <c r="C35" s="58"/>
       <c r="D35" s="55"/>
       <c r="E35" s="25" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F35" s="45"/>
       <c r="G35" s="45">
@@ -18755,11 +19717,11 @@
         <v>0</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D36" s="55"/>
       <c r="E36" s="25" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="45">
@@ -18775,11 +19737,11 @@
         <v>0</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D37" s="55"/>
       <c r="E37" s="25" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="45">
@@ -18797,7 +19759,7 @@
       <c r="C38" s="55"/>
       <c r="D38" s="55"/>
       <c r="E38" s="25" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="45">
@@ -18815,7 +19777,7 @@
       <c r="C39" s="55"/>
       <c r="D39" s="55"/>
       <c r="E39" s="25" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="55"/>
@@ -18831,11 +19793,11 @@
         <v>0</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D40" s="55"/>
       <c r="E40" s="25" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="45">
@@ -18851,11 +19813,11 @@
         <v>0</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D41" s="55"/>
       <c r="E41" s="25" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="45">
@@ -18871,11 +19833,11 @@
         <v>0</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D42" s="55"/>
       <c r="E42" s="25" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="45">
@@ -18893,7 +19855,7 @@
       <c r="C43" s="55"/>
       <c r="D43" s="55"/>
       <c r="E43" s="25" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="45">
@@ -18911,7 +19873,7 @@
       <c r="C44" s="55"/>
       <c r="D44" s="55"/>
       <c r="E44" s="25" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="45">
@@ -18934,7 +19896,7 @@
       <c r="C46" s="32"/>
       <c r="D46" s="32"/>
       <c r="E46" s="33" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
@@ -18950,10 +19912,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="F47" s="32"/>
       <c r="G47" s="32">
@@ -18969,7 +19931,7 @@
         <v>2</v>
       </c>
       <c r="E48" s="35" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="F48" s="32"/>
       <c r="G48" s="32">
@@ -18989,7 +19951,7 @@
       </c>
       <c r="D49" s="32"/>
       <c r="E49" s="33" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="F49" s="32"/>
       <c r="G49" s="32">
@@ -19005,7 +19967,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="F50" s="32"/>
       <c r="G50" s="32">
@@ -19025,7 +19987,7 @@
       </c>
       <c r="D51" s="32"/>
       <c r="E51" s="33" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="F51" s="32"/>
       <c r="G51" s="32">
@@ -19043,7 +20005,7 @@
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
       <c r="E52" s="33" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="F52" s="32"/>
       <c r="G52" s="32">
@@ -19063,7 +20025,7 @@
       </c>
       <c r="D53" s="32"/>
       <c r="E53" s="33" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="F53" s="32"/>
       <c r="G53" s="32">
@@ -19079,7 +20041,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="35" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="F54" s="32"/>
       <c r="G54" s="32">
@@ -19098,7 +20060,7 @@
         <v>213</v>
       </c>
       <c r="E55" s="57" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="F55" s="32"/>
       <c r="G55" s="32">
@@ -19117,7 +20079,7 @@
         <v>207</v>
       </c>
       <c r="E56" s="57" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="F56" s="32"/>
       <c r="G56" s="32">
@@ -19133,11 +20095,11 @@
         <v>0</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D57" s="32"/>
       <c r="E57" s="57" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="F57" s="32"/>
       <c r="G57" s="32">
@@ -19153,11 +20115,11 @@
         <v>0</v>
       </c>
       <c r="C58" s="32" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D58" s="32"/>
       <c r="E58" s="57" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F58" s="32"/>
       <c r="G58" s="32">
@@ -19173,11 +20135,11 @@
         <v>0</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D59" s="32"/>
       <c r="E59" s="33" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="F59" s="32"/>
       <c r="G59" s="32">
@@ -19195,7 +20157,7 @@
       <c r="C60" s="32"/>
       <c r="D60" s="32"/>
       <c r="E60" s="57" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="F60" s="32"/>
       <c r="G60" s="32">
@@ -19231,11 +20193,11 @@
         <v>0</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D62" s="32"/>
       <c r="E62" s="33" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="F62" s="32"/>
       <c r="G62" s="32">
@@ -19251,7 +20213,7 @@
       <c r="C63" s="32"/>
       <c r="D63" s="32"/>
       <c r="E63" s="36" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="F63" s="32"/>
       <c r="G63" s="32">
@@ -19271,7 +20233,7 @@
       </c>
       <c r="D64" s="32"/>
       <c r="E64" s="33" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="F64" s="32"/>
       <c r="G64" s="32">
@@ -19291,7 +20253,7 @@
       </c>
       <c r="D65" s="32"/>
       <c r="E65" s="33" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="F65" s="32"/>
       <c r="G65" s="32">
@@ -19309,7 +20271,7 @@
       <c r="C66" s="32"/>
       <c r="D66" s="32"/>
       <c r="E66" s="33" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="F66" s="32"/>
       <c r="G66" s="32">
@@ -19329,7 +20291,7 @@
       </c>
       <c r="D67" s="32"/>
       <c r="E67" s="36" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="F67" s="32"/>
       <c r="G67" s="32">
@@ -19347,7 +20309,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="33" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32">
@@ -19366,7 +20328,7 @@
         <v>213</v>
       </c>
       <c r="E69" s="36" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32">
@@ -19384,7 +20346,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="33" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32">
@@ -19402,7 +20364,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="33" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32">
@@ -19421,7 +20383,7 @@
         <v>207</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32">
@@ -19439,7 +20401,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="36" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32">
@@ -19455,7 +20417,7 @@
         <v>2</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -19473,7 +20435,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="36" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32">
@@ -19489,11 +20451,11 @@
         <v>0</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D76" s="32"/>
       <c r="E76" s="36" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32">
@@ -19509,11 +20471,11 @@
         <v>0</v>
       </c>
       <c r="C77" s="32" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D77" s="32"/>
       <c r="E77" s="33" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32">
@@ -19531,7 +20493,7 @@
       <c r="C78" s="32"/>
       <c r="D78" s="32"/>
       <c r="E78" s="33" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="F78" s="32"/>
       <c r="G78" s="32"/>
@@ -19547,11 +20509,11 @@
         <v>0</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D79" s="32"/>
       <c r="E79" s="33" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="F79" s="32"/>
       <c r="G79" s="32">
@@ -19567,11 +20529,11 @@
         <v>0</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D80" s="32"/>
       <c r="E80" s="33" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="F80" s="32"/>
       <c r="G80" s="32">
@@ -19590,7 +20552,7 @@
         <v>202</v>
       </c>
       <c r="E81" s="36" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="F81" s="32"/>
       <c r="G81" s="32">
@@ -19610,7 +20572,7 @@
       </c>
       <c r="D82" s="32"/>
       <c r="E82" s="33" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="F82" s="32"/>
       <c r="G82" s="32">
@@ -19628,7 +20590,7 @@
       <c r="C83" s="32"/>
       <c r="D83" s="32"/>
       <c r="E83" s="33" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="F83" s="32"/>
       <c r="G83" s="32">
@@ -19646,7 +20608,7 @@
       <c r="C84" s="32"/>
       <c r="D84" s="32"/>
       <c r="E84" s="33" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="F84" s="32"/>
       <c r="G84" s="32">
@@ -20209,13 +21171,13 @@
         <v>43400</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="E2" s="33"/>
       <c r="F2" s="32">
@@ -20223,7 +21185,7 @@
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20241,7 +21203,7 @@
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20256,10 +21218,10 @@
       <c r="E4" s="33"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20267,13 +21229,13 @@
         <v>43402</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E5" s="33"/>
       <c r="F5" s="32">
@@ -20281,7 +21243,7 @@
       </c>
       <c r="G5" s="32"/>
       <c r="H5" s="32" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20289,13 +21251,13 @@
         <v>43402</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E6" s="33"/>
       <c r="F6" s="32">
@@ -20303,7 +21265,7 @@
       </c>
       <c r="G6" s="32"/>
       <c r="H6" s="32" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="66" x14ac:dyDescent="0.3">
@@ -20311,13 +21273,13 @@
         <v>43403</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="32">
@@ -20325,7 +21287,7 @@
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20343,7 +21305,7 @@
       </c>
       <c r="G8" s="32"/>
       <c r="H8" s="32" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -20358,10 +21320,10 @@
       <c r="E9" s="33"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -20376,10 +21338,10 @@
       <c r="E10" s="33"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
@@ -20387,21 +21349,21 @@
         <v>43406</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="E11" s="33"/>
       <c r="F11" s="32"/>
       <c r="G11" s="53" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20416,10 +21378,10 @@
       <c r="E12" s="33"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20447,13 +21409,13 @@
         <v>43500</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="32">
@@ -20461,7 +21423,7 @@
       </c>
       <c r="G15" s="32"/>
       <c r="H15" s="32" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20479,7 +21441,7 @@
       </c>
       <c r="G16" s="32"/>
       <c r="H16" s="32" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20494,10 +21456,10 @@
       <c r="E17" s="33"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20505,13 +21467,13 @@
         <v>43502</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="32">
@@ -20519,7 +21481,7 @@
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="32" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20527,13 +21489,13 @@
         <v>43502</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="32">
@@ -20541,7 +21503,7 @@
       </c>
       <c r="G19" s="32"/>
       <c r="H19" s="32" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -20556,10 +21518,10 @@
       <c r="E20" s="33"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
@@ -20567,21 +21529,21 @@
         <v>43504</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="32"/>
       <c r="G21" s="53" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -20596,10 +21558,10 @@
       <c r="E22" s="33"/>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
